--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884-csk.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884-csk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DFBCE7-217D-4C73-B696-F49C650CEEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74A5EEC-D580-4269-8267-4213BF841053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -549,20 +549,6 @@
   <dxfs count="2">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -586,6 +572,20 @@
       </fill>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -600,14 +600,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DataTable" displayName="DataTable" ref="A1:J99" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DataTable" displayName="DataTable" ref="A1:J99" headerRowDxfId="1">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="губ"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="чр-г-м"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="чр-г-ж"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="чр-у-м"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="чр-с-ж"/>
-    <tableColumn id="10" xr3:uid="{5592BEEA-7272-4EBE-B648-ADB6AA541532}" name=" " dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{5592BEEA-7272-4EBE-B648-ADB6AA541532}" name=" " dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="чу-г-м"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="чу-г-ж"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="чу-у-м"/>
